--- a/docs/sample_kb/excel/办公设备采购清单与库存表.xlsx
+++ b/docs/sample_kb/excel/办公设备采购清单与库存表.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="设备库存明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="固定资产折旧表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="采购申请记录" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +451,11 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
@@ -482,7 +489,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>高阶开发专用机</t>
+          <t>在库</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>研发高阶专用机</t>
         </is>
       </c>
     </row>
@@ -515,6 +527,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>在库</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>标准双屏配置</t>
         </is>
       </c>
@@ -548,6 +565,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>在库</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>特批健康座椅</t>
         </is>
       </c>
@@ -581,6 +603,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>在库</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>商务出差笔记本</t>
         </is>
       </c>
@@ -614,7 +641,402 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>在库</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>标准外设库房</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DEV-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mac Studio</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>M2 Ultra / 64G / 2TB</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>31999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>设计部</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>在库</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3D渲染工作站</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DEV-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dell PowerEdge R760</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>服务器 2x Xeon 6430 / 256G</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>85000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IT运维部</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>运行中</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>IDC 本地测试节点</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>资产编号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>资产名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>购置日期</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>原值(元)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>残值率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>折旧年限</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>月折旧额(元)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>资产净值(元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AST-2024-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MacBook Pro 集体采购</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>275988</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7283.02</v>
+      </c>
+      <c r="H2" t="n">
+        <v>145660.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AST-2024-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dell 显示器批次 A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2024-03-10</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>97972</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1938.61</v>
+      </c>
+      <c r="H3" t="n">
+        <v>48465.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AST-2025-001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IDC 服务器节点集群</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>255000</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4037.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>218625</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>采购单号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>申请人</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>申请部门</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>采购物品</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>估算金额(元)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>审批状态</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>供应商</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PO-2026-0101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IT运维部</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>显示器 10 台</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>34990</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>戴尔中国有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PO-2026-0102</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>李娜</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>研发部</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MacBook Pro 5 台</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>114995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>苹果电脑贸易(上海)有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PO-2026-0103</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王强</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>行政部</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>人体工学椅 3 把</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>29400</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>审批中</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>赫曼米勒家具(上海)有限公司</t>
         </is>
       </c>
     </row>
